--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$99</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3536" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3839" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:33:27+00:00</t>
+    <t>2023-11-17T15:40:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -343,13 +343,196 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Observation.implicitRules</t>
+    <t>Observation.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Observation.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Observation.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Observation.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Observation.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>Observation.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -360,9 +543,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>Observation.language</t>
@@ -445,38 +625,10 @@
     <t>Observation.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Observation.extension:supportingInfoAdministrationOxygen</t>
@@ -620,26 +772,7 @@
     <t>Observation.partOf.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Observation.partOf.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.partOf.reference</t>
@@ -672,9 +805,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -826,10 +956,6 @@
     <t>Observation.category.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
     <t>Code defined by a terminology system</t>
   </si>
   <si>
@@ -1273,10 +1399,6 @@
     <t>Observation.issued</t>
   </si>
   <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
     <t>Date/Time this version was made available</t>
   </si>
   <si>
@@ -1629,9 +1751,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -2383,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP91"/>
+  <dimension ref="A1:AP99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.234375" customWidth="true" bestFit="true"/>
@@ -2410,7 +2529,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="85.6640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2937,10 +3056,10 @@
         <v>80</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>107</v>
@@ -2951,9 +3070,7 @@
       <c r="M5" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>80</v>
@@ -3002,7 +3119,7 @@
         <v>80</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -3011,10 +3128,10 @@
         <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>80</v>
@@ -3026,7 +3143,7 @@
         <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>80</v>
@@ -3037,21 +3154,21 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>80</v>
@@ -3098,28 +3215,28 @@
         <v>80</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AD6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>121</v>
@@ -3128,13 +3245,13 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>80</v>
@@ -3146,7 +3263,7 @@
         <v>80</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>80</v>
@@ -3157,14 +3274,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -3180,19 +3297,19 @@
         <v>80</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>127</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3242,7 +3359,7 @@
         <v>80</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -3266,7 +3383,7 @@
         <v>80</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>80</v>
@@ -3277,21 +3394,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>80</v>
@@ -3300,19 +3417,19 @@
         <v>80</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3362,19 +3479,19 @@
         <v>80</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>80</v>
@@ -3386,7 +3503,7 @@
         <v>80</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>80</v>
@@ -3397,21 +3514,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>80</v>
@@ -3420,19 +3537,19 @@
         <v>80</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3470,31 +3587,31 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>80</v>
@@ -3506,7 +3623,7 @@
         <v>80</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>80</v>
@@ -3517,23 +3634,21 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
@@ -3542,19 +3657,19 @@
         <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3604,7 +3719,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3616,7 +3731,7 @@
         <v>103</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>80</v>
@@ -3628,7 +3743,7 @@
         <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>80</v>
@@ -3639,14 +3754,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>80</v>
       </c>
@@ -3655,7 +3768,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>80</v>
@@ -3664,18 +3777,20 @@
         <v>80</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>80</v>
@@ -3700,13 +3815,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3724,7 +3839,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3736,7 +3851,7 @@
         <v>103</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>80</v>
@@ -3745,10 +3860,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3766,7 +3881,7 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3779,13 +3894,13 @@
         <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="J12" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>158</v>
@@ -3794,11 +3909,9 @@
         <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O12" t="s" s="2">
         <v>160</v>
       </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
       </c>
@@ -3822,31 +3935,31 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>80</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3858,7 +3971,7 @@
         <v>103</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>80</v>
@@ -3867,10 +3980,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3881,10 +3994,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3895,30 +4008,30 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3966,13 +4079,13 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>103</v>
@@ -3981,19 +4094,19 @@
         <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -4001,21 +4114,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
@@ -4024,23 +4137,21 @@
         <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
       </c>
@@ -4064,13 +4175,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4088,31 +4199,31 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -4123,14 +4234,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4140,25 +4251,25 @@
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4208,31 +4319,31 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4243,21 +4354,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -4269,15 +4380,17 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -4326,13 +4439,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -4350,7 +4463,7 @@
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
@@ -4361,14 +4474,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4387,16 +4500,16 @@
         <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4434,19 +4547,19 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4458,7 +4571,7 @@
         <v>103</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>80</v>
@@ -4481,14 +4594,16 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4504,10 +4619,10 @@
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>200</v>
@@ -4516,7 +4631,7 @@
         <v>201</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4566,19 +4681,19 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>80</v>
@@ -4601,12 +4716,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4624,20 +4741,18 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>107</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -4662,13 +4777,13 @@
         <v>80</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>211</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>80</v>
@@ -4686,19 +4801,19 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
@@ -4710,7 +4825,7 @@
         <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
@@ -4721,44 +4836,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4794,31 +4911,31 @@
         <v>80</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>80</v>
@@ -4827,10 +4944,10 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>105</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -4841,10 +4958,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4855,7 +4972,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -4867,18 +4984,18 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4926,13 +5043,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>103</v>
@@ -4941,19 +5058,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>80</v>
+        <v>217</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>105</v>
+        <v>218</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4961,45 +5078,45 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>222</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5024,13 +5141,13 @@
         <v>80</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>80</v>
@@ -5048,34 +5165,34 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>80</v>
@@ -5083,21 +5200,21 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>92</v>
@@ -5106,23 +5223,21 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -5146,29 +5261,31 @@
         <v>80</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5180,22 +5297,22 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -5203,26 +5320,24 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -5231,20 +5346,16 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>239</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
       </c>
@@ -5268,13 +5379,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5292,19 +5403,19 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>110</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
@@ -5313,13 +5424,13 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>111</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5327,21 +5438,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -5353,15 +5464,17 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5398,31 +5511,31 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>121</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>80</v>
@@ -5434,7 +5547,7 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>80</v>
@@ -5445,21 +5558,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -5468,19 +5581,19 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5518,31 +5631,31 @@
         <v>80</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>198</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>103</v>
+        <v>247</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>80</v>
@@ -5565,10 +5678,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5576,13 +5689,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G27" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H27" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -5591,20 +5704,18 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
       </c>
@@ -5628,13 +5739,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>253</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -5652,13 +5763,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>103</v>
@@ -5673,10 +5784,10 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>105</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>80</v>
@@ -5687,10 +5798,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5710,18 +5821,20 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -5770,7 +5883,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5779,10 +5892,10 @@
         <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5791,10 +5904,10 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>112</v>
+        <v>261</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -5805,21 +5918,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5828,19 +5941,19 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>140</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>142</v>
+        <v>265</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5878,31 +5991,31 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5925,10 +6038,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5945,32 +6058,32 @@
         <v>92</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>276</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>80</v>
@@ -5988,13 +6101,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>80</v>
+        <v>272</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -6012,10 +6125,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>91</v>
@@ -6027,19 +6140,19 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>80</v>
@@ -6050,7 +6163,7 @@
         <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6058,22 +6171,22 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>282</v>
@@ -6084,7 +6197,9 @@
       <c r="N31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
       </c>
@@ -6108,37 +6223,35 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>103</v>
@@ -6153,13 +6266,13 @@
         <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>80</v>
@@ -6167,12 +6280,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D32" t="s" s="2">
         <v>80</v>
       </c>
@@ -6190,29 +6305,29 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -6230,13 +6345,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>287</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -6254,13 +6369,13 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>103</v>
@@ -6275,13 +6390,13 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -6289,10 +6404,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6312,23 +6427,19 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>80</v>
       </c>
@@ -6337,7 +6448,7 @@
         <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>80</v>
@@ -6376,7 +6487,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6385,10 +6496,10 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -6397,10 +6508,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6411,21 +6522,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>80</v>
@@ -6434,23 +6545,21 @@
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>308</v>
+        <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>309</v>
+        <v>115</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>310</v>
+        <v>116</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6486,31 +6595,31 @@
         <v>80</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>121</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -6519,10 +6628,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>315</v>
+        <v>105</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6533,10 +6642,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6544,13 +6653,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
@@ -6559,19 +6668,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6620,13 +6729,13 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>103</v>
@@ -6641,10 +6750,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6655,46 +6764,42 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>239</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>108</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6718,13 +6823,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6742,56 +6847,56 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>110</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6803,15 +6908,17 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6848,31 +6955,31 @@
         <v>80</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>195</v>
+        <v>121</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6884,7 +6991,7 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6895,50 +7002,52 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>140</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>197</v>
+        <v>314</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>316</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>80</v>
@@ -6968,31 +7077,31 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>198</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -7001,10 +7110,10 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -7015,10 +7124,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7029,7 +7138,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>80</v>
@@ -7041,20 +7150,18 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -7090,23 +7197,25 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AC39" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>263</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>103</v>
@@ -7121,10 +7230,10 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>265</v>
+        <v>328</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -7135,14 +7244,12 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>80</v>
       </c>
@@ -7154,7 +7261,7 @@
         <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
@@ -7163,26 +7270,26 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>258</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>260</v>
+        <v>332</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>261</v>
+        <v>333</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>80</v>
@@ -7224,13 +7331,13 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>103</v>
@@ -7245,10 +7352,10 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>265</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -7259,10 +7366,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7282,19 +7389,23 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>193</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -7303,7 +7414,7 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>80</v>
+        <v>335</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>80</v>
@@ -7342,7 +7453,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>195</v>
+        <v>344</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7351,10 +7462,10 @@
         <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -7363,10 +7474,10 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>112</v>
+        <v>346</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7384,14 +7495,14 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -7400,21 +7511,23 @@
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>349</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>140</v>
+        <v>350</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>197</v>
+        <v>351</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
@@ -7450,31 +7563,31 @@
         <v>80</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>198</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7483,10 +7596,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>105</v>
+        <v>356</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7497,10 +7610,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7508,7 +7621,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>91</v>
@@ -7526,23 +7639,23 @@
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>272</v>
+        <v>359</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>273</v>
+        <v>360</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>274</v>
+        <v>361</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>80</v>
@@ -7584,7 +7697,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7605,10 +7718,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7619,24 +7732,24 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>367</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>80</v>
@@ -7645,18 +7758,20 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
@@ -7680,13 +7795,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>80</v>
+        <v>373</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7704,10 +7819,10 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>91</v>
@@ -7719,30 +7834,30 @@
         <v>104</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>286</v>
+        <v>376</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>80</v>
+        <v>378</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7750,7 +7865,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>91</v>
@@ -7762,29 +7877,25 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>356</v>
+        <v>80</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>80</v>
@@ -7826,7 +7937,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>295</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7835,10 +7946,10 @@
         <v>91</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -7847,10 +7958,10 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -7861,21 +7972,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -7884,23 +7995,21 @@
         <v>80</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>192</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>301</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7936,31 +8045,31 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>303</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -7969,10 +8078,10 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>304</v>
+        <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>305</v>
+        <v>105</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7983,10 +8092,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7997,7 +8106,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -8009,19 +8118,19 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>308</v>
+        <v>147</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>80</v>
@@ -8058,25 +8167,23 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>103</v>
@@ -8091,10 +8198,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -8105,18 +8212,20 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>91</v>
@@ -8131,19 +8240,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8192,13 +8301,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>103</v>
@@ -8213,10 +8322,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -8227,10 +8336,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8238,35 +8347,31 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>363</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -8314,7 +8419,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>110</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8323,25 +8428,25 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>368</v>
+        <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>369</v>
+        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>111</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -8349,14 +8454,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8372,19 +8477,19 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>373</v>
+        <v>114</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>116</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>376</v>
+        <v>117</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8422,19 +8527,19 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8446,7 +8551,7 @@
         <v>103</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>80</v>
@@ -8455,13 +8560,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>377</v>
+        <v>105</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>371</v>
+        <v>80</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8469,18 +8574,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>91</v>
@@ -8495,26 +8600,26 @@
         <v>92</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>380</v>
+        <v>135</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>381</v>
+        <v>313</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>383</v>
+        <v>315</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>384</v>
+        <v>316</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
-        <v>80</v>
+        <v>392</v>
       </c>
       <c r="S51" t="s" s="2">
         <v>80</v>
@@ -8556,7 +8661,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>318</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8568,22 +8673,22 @@
         <v>103</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>386</v>
+        <v>319</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>387</v>
+        <v>320</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>388</v>
+        <v>80</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>80</v>
@@ -8591,24 +8696,24 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
@@ -8617,20 +8722,18 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>391</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>392</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
@@ -8678,7 +8781,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8687,25 +8790,25 @@
         <v>91</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>396</v>
+        <v>103</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>397</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>398</v>
+        <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>399</v>
+        <v>327</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>401</v>
+        <v>80</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>80</v>
@@ -8713,10 +8816,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8724,7 +8827,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>91</v>
@@ -8739,24 +8842,26 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>403</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
-        <v>80</v>
+        <v>397</v>
       </c>
       <c r="S53" t="s" s="2">
         <v>80</v>
@@ -8798,7 +8903,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>402</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8819,13 +8924,13 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>337</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>80</v>
@@ -8833,10 +8938,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8847,7 +8952,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -8859,19 +8964,19 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>412</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>413</v>
+        <v>342</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>176</v>
+        <v>333</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>414</v>
+        <v>343</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8920,34 +9025,34 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>410</v>
+        <v>344</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>415</v>
+        <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>416</v>
+        <v>345</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>417</v>
+        <v>346</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>418</v>
+        <v>80</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>80</v>
@@ -8955,10 +9060,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8972,7 +9077,7 @@
         <v>91</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
@@ -8981,19 +9086,19 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>420</v>
+        <v>349</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>421</v>
+        <v>351</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>423</v>
+        <v>353</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9030,17 +9135,19 @@
         <v>80</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>419</v>
+        <v>354</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9049,7 +9156,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9058,31 +9165,29 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>428</v>
+        <v>355</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>429</v>
+        <v>356</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>80</v>
       </c>
@@ -9094,7 +9199,7 @@
         <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -9103,19 +9208,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>359</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
+        <v>360</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>422</v>
+        <v>361</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>423</v>
+        <v>362</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9164,7 +9269,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>363</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9173,7 +9278,7 @@
         <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>426</v>
+        <v>103</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9182,27 +9287,27 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>428</v>
+        <v>364</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>429</v>
+        <v>365</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9210,31 +9315,35 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>192</v>
+        <v>404</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>193</v>
+        <v>405</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>408</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
       </c>
@@ -9282,7 +9391,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>195</v>
+        <v>403</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9291,25 +9400,25 @@
         <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>112</v>
+        <v>411</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>80</v>
@@ -9317,14 +9426,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>413</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9340,19 +9449,19 @@
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>414</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>140</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>197</v>
+        <v>416</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>142</v>
+        <v>417</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9390,19 +9499,19 @@
         <v>80</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>198</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9414,7 +9523,7 @@
         <v>103</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -9423,13 +9532,13 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>80</v>
+        <v>376</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>105</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>80</v>
+        <v>412</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>80</v>
@@ -9437,24 +9546,24 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>80</v>
@@ -9463,19 +9572,19 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -9524,7 +9633,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9536,22 +9645,22 @@
         <v>103</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>80</v>
@@ -9559,52 +9668,50 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>114</v>
+        <v>432</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>292</v>
+        <v>435</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q60" t="s" s="2">
-        <v>453</v>
-      </c>
+      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>80</v>
       </c>
@@ -9624,13 +9731,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>455</v>
+        <v>80</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -9648,7 +9755,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9657,25 +9764,25 @@
         <v>91</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>103</v>
+        <v>437</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>438</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>80</v>
@@ -9683,10 +9790,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9694,13 +9801,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>80</v>
@@ -9709,20 +9816,18 @@
         <v>92</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
       </c>
@@ -9770,7 +9875,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9791,13 +9896,13 @@
         <v>80</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>80</v>
@@ -9805,10 +9910,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9816,13 +9921,13 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>80</v>
@@ -9831,26 +9936,26 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>471</v>
+        <v>225</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>473</v>
+        <v>80</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>80</v>
@@ -9892,34 +9997,34 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>475</v>
+        <v>103</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>80</v>
+        <v>455</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>80</v>
@@ -9927,10 +10032,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9938,7 +10043,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>91</v>
@@ -9953,26 +10058,26 @@
         <v>92</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>460</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
-        <v>482</v>
+        <v>80</v>
       </c>
       <c r="S63" t="s" s="2">
         <v>80</v>
@@ -10002,19 +10107,17 @@
         <v>80</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="AC63" s="2"/>
       <c r="AD63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>80</v>
+        <v>465</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10023,7 +10126,7 @@
         <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>103</v>
+        <v>466</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>104</v>
@@ -10032,29 +10135,31 @@
         <v>80</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>80</v>
       </c>
@@ -10072,22 +10177,22 @@
         <v>80</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>239</v>
+        <v>473</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10112,13 +10217,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -10136,7 +10241,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10145,7 +10250,7 @@
         <v>91</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>104</v>
@@ -10154,38 +10259,38 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>80</v>
+        <v>467</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>105</v>
+        <v>468</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>80</v>
@@ -10197,20 +10302,16 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>239</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>80</v>
       </c>
@@ -10234,13 +10335,13 @@
         <v>80</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>80</v>
@@ -10258,49 +10359,49 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>494</v>
+        <v>110</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>502</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>503</v>
+        <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>504</v>
+        <v>111</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>505</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10319,20 +10420,18 @@
         <v>80</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>507</v>
+        <v>114</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>508</v>
+        <v>115</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>509</v>
+        <v>116</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>511</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>80</v>
       </c>
@@ -10368,19 +10467,19 @@
         <v>80</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>506</v>
+        <v>121</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10392,7 +10491,7 @@
         <v>103</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>80</v>
@@ -10401,10 +10500,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>512</v>
+        <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>513</v>
+        <v>105</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10415,10 +10514,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>479</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10426,33 +10525,35 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>239</v>
+        <v>480</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>515</v>
+        <v>481</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>482</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
       </c>
@@ -10476,13 +10577,13 @@
         <v>80</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>519</v>
+        <v>80</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>520</v>
+        <v>80</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10500,7 +10601,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>514</v>
+        <v>485</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10518,27 +10619,27 @@
         <v>80</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>521</v>
+        <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>522</v>
+        <v>486</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>523</v>
+        <v>487</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>524</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>525</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>525</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10552,33 +10653,35 @@
         <v>91</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I68" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="J68" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>526</v>
+        <v>490</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>527</v>
+        <v>491</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>528</v>
+        <v>333</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>529</v>
+        <v>492</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>80</v>
       </c>
@@ -10598,13 +10701,13 @@
         <v>80</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>518</v>
+        <v>272</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>530</v>
+        <v>494</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>80</v>
@@ -10622,7 +10725,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>496</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10643,10 +10746,10 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>532</v>
+        <v>497</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>533</v>
+        <v>498</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10657,10 +10760,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>534</v>
+        <v>499</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>534</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10668,33 +10771,35 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>535</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>536</v>
+        <v>501</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>537</v>
+        <v>502</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
       </c>
@@ -10742,7 +10847,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>534</v>
+        <v>504</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10754,33 +10859,33 @@
         <v>103</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>539</v>
+        <v>80</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>540</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>541</v>
+        <v>506</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>542</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>543</v>
+        <v>508</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10788,39 +10893,41 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>544</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>80</v>
@@ -10862,7 +10969,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10871,36 +10978,36 @@
         <v>91</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>103</v>
+        <v>515</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>548</v>
+        <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>549</v>
+        <v>505</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>551</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>552</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>552</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10908,41 +11015,41 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>553</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>554</v>
+        <v>519</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>80</v>
+        <v>522</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>80</v>
@@ -10984,19 +11091,19 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>558</v>
+        <v>104</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>80</v>
@@ -11005,10 +11112,10 @@
         <v>80</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>559</v>
+        <v>505</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>560</v>
+        <v>524</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
@@ -11019,10 +11126,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>561</v>
+        <v>525</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11036,7 +11143,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
@@ -11045,16 +11152,20 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>193</v>
+        <v>526</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
       </c>
@@ -11078,13 +11189,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>80</v>
+        <v>531</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -11102,7 +11213,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>195</v>
+        <v>525</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11111,10 +11222,10 @@
         <v>91</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>80</v>
+        <v>532</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>80</v>
@@ -11123,10 +11234,10 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>112</v>
+        <v>533</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -11137,14 +11248,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>138</v>
+        <v>535</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11163,18 +11274,20 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>140</v>
+        <v>536</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>197</v>
+        <v>537</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
       </c>
@@ -11198,31 +11311,31 @@
         <v>80</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>80</v>
+        <v>540</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>80</v>
+        <v>541</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>198</v>
+        <v>534</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11234,37 +11347,37 @@
         <v>103</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>80</v>
+        <v>543</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>564</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11277,25 +11390,25 @@
         <v>80</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>139</v>
+        <v>547</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>142</v>
+        <v>550</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>160</v>
+        <v>551</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>80</v>
@@ -11344,7 +11457,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11356,7 +11469,7 @@
         <v>103</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
@@ -11365,10 +11478,10 @@
         <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>80</v>
+        <v>552</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>105</v>
+        <v>553</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
@@ -11379,10 +11492,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11405,16 +11518,16 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>569</v>
+        <v>281</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11440,13 +11553,13 @@
         <v>80</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>80</v>
+        <v>559</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>80</v>
@@ -11464,7 +11577,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11473,36 +11586,36 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>573</v>
+        <v>103</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>574</v>
+        <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>80</v>
+        <v>560</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>80</v>
+        <v>563</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11516,7 +11629,7 @@
         <v>91</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>80</v>
@@ -11525,18 +11638,20 @@
         <v>80</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>569</v>
+        <v>281</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
       </c>
@@ -11560,13 +11675,13 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>80</v>
+        <v>569</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>80</v>
+        <v>570</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11584,7 +11699,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11593,10 +11708,10 @@
         <v>91</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>573</v>
+        <v>103</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>574</v>
+        <v>104</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>80</v>
@@ -11605,10 +11720,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11619,10 +11734,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11645,20 +11760,18 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>239</v>
+        <v>574</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11682,13 +11795,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>586</v>
+        <v>80</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11706,7 +11819,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11718,33 +11831,33 @@
         <v>103</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>504</v>
+        <v>580</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11755,7 +11868,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11767,20 +11880,18 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>239</v>
+        <v>583</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>80</v>
       </c>
@@ -11804,13 +11915,13 @@
         <v>80</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>518</v>
+        <v>80</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>595</v>
+        <v>80</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>596</v>
+        <v>80</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>80</v>
@@ -11828,45 +11939,45 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM78" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AM78" t="s" s="2">
+      <c r="AN78" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AN78" t="s" s="2">
-        <v>504</v>
-      </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11877,7 +11988,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>80</v>
@@ -11889,19 +12000,19 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -11950,19 +12061,19 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11971,10 +12082,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11985,10 +12096,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12011,17 +12122,15 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>607</v>
+        <v>108</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>292</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12070,7 +12179,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>606</v>
+        <v>110</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12079,10 +12188,10 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12091,10 +12200,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>575</v>
+        <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>609</v>
+        <v>111</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12105,14 +12214,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12128,19 +12237,19 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>611</v>
+        <v>114</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>612</v>
+        <v>115</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>613</v>
+        <v>116</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>614</v>
+        <v>117</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12178,19 +12287,19 @@
         <v>80</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>610</v>
+        <v>121</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12202,7 +12311,7 @@
         <v>103</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>80</v>
@@ -12211,10 +12320,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>616</v>
+        <v>105</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12225,14 +12334,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>617</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>80</v>
+        <v>603</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12245,24 +12354,26 @@
         <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>618</v>
+        <v>114</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>619</v>
+        <v>604</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>620</v>
+        <v>605</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
       </c>
@@ -12310,7 +12421,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12322,7 +12433,7 @@
         <v>103</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -12331,10 +12442,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>615</v>
+        <v>80</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>622</v>
+        <v>105</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12345,10 +12456,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12359,32 +12470,30 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>553</v>
+        <v>608</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>626</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>80</v>
       </c>
@@ -12432,19 +12541,19 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>103</v>
+        <v>612</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12453,10 +12562,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12467,10 +12576,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12493,15 +12602,17 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>192</v>
+        <v>608</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>193</v>
+        <v>617</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>80</v>
@@ -12550,7 +12661,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>195</v>
+        <v>616</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12559,10 +12670,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>80</v>
+        <v>612</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>80</v>
+        <v>613</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
@@ -12571,10 +12682,10 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>80</v>
+        <v>614</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>112</v>
+        <v>619</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12585,21 +12696,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12611,18 +12722,20 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>140</v>
+        <v>621</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>197</v>
+        <v>622</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>624</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
       </c>
@@ -12646,55 +12759,55 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>80</v>
+        <v>625</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>80</v>
+        <v>626</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>198</v>
+        <v>620</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>80</v>
+        <v>627</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>80</v>
+        <v>628</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12705,14 +12818,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>564</v>
+        <v>80</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12725,25 +12838,25 @@
         <v>80</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>281</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>565</v>
+        <v>630</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>566</v>
+        <v>631</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>142</v>
+        <v>632</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>160</v>
+        <v>633</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12768,13 +12881,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>80</v>
+        <v>634</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>80</v>
+        <v>635</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12792,7 +12905,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>567</v>
+        <v>629</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12804,19 +12917,19 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>80</v>
+        <v>627</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>80</v>
+        <v>628</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12827,10 +12940,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12838,34 +12951,34 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>239</v>
+        <v>637</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -12890,13 +13003,13 @@
         <v>80</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12914,10 +13027,10 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>91</v>
@@ -12926,22 +13039,22 @@
         <v>103</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>104</v>
+        <v>642</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>638</v>
+        <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>335</v>
+        <v>643</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>336</v>
+        <v>644</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>80</v>
@@ -12949,10 +13062,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12966,29 +13079,27 @@
         <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>420</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
       </c>
@@ -13012,13 +13123,13 @@
         <v>80</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>643</v>
+        <v>80</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>644</v>
+        <v>80</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>80</v>
@@ -13036,7 +13147,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13045,7 +13156,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>645</v>
+        <v>103</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>104</v>
@@ -13054,27 +13165,27 @@
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>646</v>
+        <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>428</v>
+        <v>614</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>429</v>
+        <v>648</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>430</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13085,32 +13196,30 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J89" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K89" t="s" s="2">
-        <v>239</v>
+        <v>650</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13134,13 +13243,13 @@
         <v>80</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>80</v>
@@ -13158,19 +13267,19 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>651</v>
+        <v>103</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>80</v>
@@ -13179,10 +13288,10 @@
         <v>80</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>105</v>
+        <v>654</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>493</v>
+        <v>655</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
@@ -13193,14 +13302,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>495</v>
+        <v>80</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13216,23 +13325,21 @@
         <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>239</v>
+        <v>657</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>496</v>
+        <v>658</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>497</v>
+        <v>659</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>660</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13256,13 +13363,13 @@
         <v>80</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>209</v>
+        <v>80</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>653</v>
+        <v>80</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>80</v>
@@ -13280,7 +13387,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13292,33 +13399,33 @@
         <v>103</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>502</v>
+        <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>503</v>
+        <v>654</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>504</v>
+        <v>661</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>505</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13332,28 +13439,28 @@
         <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>81</v>
+        <v>592</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>556</v>
+        <v>664</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>557</v>
+        <v>665</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -13402,7 +13509,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13411,10 +13518,10 @@
         <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>80</v>
+        <v>666</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
@@ -13423,20 +13530,990 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>559</v>
+        <v>667</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>560</v>
+        <v>668</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP91" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP99" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP91">
+  <autoFilter ref="A1:AP99">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13446,7 +14523,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI90">
+  <conditionalFormatting sqref="A2:AI98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/ig/nr-add-sato2-profile/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$110</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3839" uniqueCount="696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="706">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:40:40+00:00</t>
+    <t>2023-11-23T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1786,16 +1786,46 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J147-MethodHeartrate-ENS/FHIR/JDV-J147-MethodHeartrate-ENS</t>
   </si>
   <si>
     <t>OBX-17</t>
   </si>
   <si>
     <t>methodCode</t>
+  </si>
+  <si>
+    <t>Observation.method.id</t>
+  </si>
+  <si>
+    <t>Observation.method.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2502,7 +2532,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP99"/>
+  <dimension ref="A1:AP110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.234375" customWidth="true" bestFit="true"/>
@@ -2530,7 +2560,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.6640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="93.578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -11675,13 +11705,11 @@
         <v>80</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="Y76" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Y76" s="2"/>
+      <c r="Z76" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>80</v>
@@ -11720,10 +11748,10 @@
         <v>80</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -11734,10 +11762,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11760,17 +11788,15 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>574</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>575</v>
+        <v>108</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>577</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>80</v>
@@ -11819,7 +11845,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>573</v>
+        <v>110</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11828,47 +11854,47 @@
         <v>91</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>578</v>
+        <v>80</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>579</v>
+        <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>580</v>
+        <v>111</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>581</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
@@ -11880,16 +11906,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>583</v>
+        <v>114</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>115</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>116</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>586</v>
+        <v>117</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11927,57 +11953,57 @@
         <v>80</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>582</v>
+        <v>121</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>227</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>587</v>
+        <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>588</v>
+        <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>589</v>
+        <v>105</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>590</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11997,22 +12023,22 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>592</v>
+        <v>147</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>593</v>
+        <v>300</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>594</v>
+        <v>301</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>595</v>
+        <v>302</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>596</v>
+        <v>303</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12061,7 +12087,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>591</v>
+        <v>304</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -12073,7 +12099,7 @@
         <v>103</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>597</v>
+        <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -12082,10 +12108,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>598</v>
+        <v>305</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>599</v>
+        <v>306</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12096,10 +12122,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>600</v>
+        <v>575</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12214,10 +12240,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12334,45 +12360,45 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>603</v>
+        <v>80</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>604</v>
+        <v>313</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>605</v>
+        <v>314</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>117</v>
+        <v>315</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>209</v>
+        <v>316</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12421,19 +12447,19 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>318</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>80</v>
@@ -12442,10 +12468,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>105</v>
+        <v>320</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12456,10 +12482,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>607</v>
+        <v>578</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>607</v>
+        <v>578</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12479,19 +12505,19 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>608</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>609</v>
+        <v>323</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>610</v>
+        <v>324</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>611</v>
+        <v>325</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12541,7 +12567,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>607</v>
+        <v>326</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12550,10 +12576,10 @@
         <v>91</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>612</v>
+        <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>613</v>
+        <v>104</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12562,10 +12588,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>614</v>
+        <v>327</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>615</v>
+        <v>328</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12576,10 +12602,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>616</v>
+        <v>579</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>616</v>
+        <v>579</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12587,7 +12613,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>91</v>
@@ -12599,21 +12625,23 @@
         <v>80</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>608</v>
+        <v>171</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>617</v>
+        <v>331</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>618</v>
+        <v>332</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>80</v>
       </c>
@@ -12661,7 +12689,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>616</v>
+        <v>336</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12670,10 +12698,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>612</v>
+        <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>613</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
@@ -12682,10 +12710,10 @@
         <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>614</v>
+        <v>337</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>619</v>
+        <v>338</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
@@ -12696,10 +12724,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>620</v>
+        <v>580</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12719,22 +12747,22 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>281</v>
+        <v>107</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>621</v>
+        <v>341</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>622</v>
+        <v>342</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>623</v>
+        <v>333</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>624</v>
+        <v>343</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>80</v>
@@ -12759,13 +12787,13 @@
         <v>80</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>625</v>
+        <v>80</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>626</v>
+        <v>80</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>80</v>
@@ -12783,7 +12811,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>620</v>
+        <v>344</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12801,13 +12829,13 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>627</v>
+        <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>628</v>
+        <v>345</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>544</v>
+        <v>346</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
@@ -12818,10 +12846,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>581</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>629</v>
+        <v>581</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12832,7 +12860,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>80</v>
@@ -12841,22 +12869,22 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>281</v>
+        <v>349</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>631</v>
+        <v>351</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>632</v>
+        <v>352</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>633</v>
+        <v>353</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12881,13 +12909,13 @@
         <v>80</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>634</v>
+        <v>80</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>635</v>
+        <v>80</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>80</v>
@@ -12905,13 +12933,13 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>629</v>
+        <v>354</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>103</v>
@@ -12923,13 +12951,13 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>627</v>
+        <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>628</v>
+        <v>355</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>544</v>
+        <v>356</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12940,10 +12968,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>582</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12963,22 +12991,22 @@
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>637</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>638</v>
+        <v>359</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>639</v>
+        <v>360</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>640</v>
+        <v>361</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>641</v>
+        <v>362</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
@@ -13027,7 +13055,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>636</v>
+        <v>363</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -13039,7 +13067,7 @@
         <v>103</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>642</v>
+        <v>104</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
@@ -13048,10 +13076,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>643</v>
+        <v>364</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>644</v>
+        <v>365</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13062,10 +13090,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13088,16 +13116,16 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>646</v>
+        <v>585</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>647</v>
+        <v>586</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>333</v>
+        <v>587</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13147,7 +13175,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13159,33 +13187,33 @@
         <v>103</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>104</v>
+        <v>227</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>80</v>
+        <v>588</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>614</v>
+        <v>589</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>648</v>
+        <v>590</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>80</v>
+        <v>591</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>649</v>
+        <v>592</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>649</v>
+        <v>592</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13196,7 +13224,7 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>80</v>
@@ -13205,19 +13233,19 @@
         <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>650</v>
+        <v>593</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>651</v>
+        <v>594</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>652</v>
+        <v>595</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>653</v>
+        <v>596</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13267,13 +13295,13 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>649</v>
+        <v>592</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>103</v>
@@ -13285,27 +13313,27 @@
         <v>80</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>80</v>
+        <v>597</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>654</v>
+        <v>598</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>655</v>
+        <v>599</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>80</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13325,21 +13353,23 @@
         <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>657</v>
+        <v>602</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>658</v>
+        <v>603</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>659</v>
+        <v>604</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13387,7 +13417,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>656</v>
+        <v>601</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13399,7 +13429,7 @@
         <v>103</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>227</v>
+        <v>607</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13408,10 +13438,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>661</v>
+        <v>609</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13422,10 +13452,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>662</v>
+        <v>610</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>662</v>
+        <v>610</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13436,32 +13466,28 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>592</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>663</v>
+        <v>108</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>665</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13509,19 +13535,19 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>662</v>
+        <v>110</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>666</v>
+        <v>80</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
@@ -13530,10 +13556,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>667</v>
+        <v>80</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>668</v>
+        <v>111</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13544,21 +13570,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>669</v>
+        <v>611</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>669</v>
+        <v>611</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>80</v>
@@ -13570,15 +13596,17 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13615,31 +13643,31 @@
         <v>80</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>80</v>
@@ -13651,7 +13679,7 @@
         <v>80</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13662,14 +13690,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>670</v>
+        <v>612</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>670</v>
+        <v>612</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>113</v>
+        <v>613</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13682,24 +13710,26 @@
         <v>80</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>115</v>
+        <v>614</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>116</v>
+        <v>615</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O93" s="2"/>
+      <c r="O93" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
       </c>
@@ -13735,19 +13765,19 @@
         <v>80</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>121</v>
+        <v>616</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13782,46 +13812,44 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>671</v>
+        <v>617</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>671</v>
+        <v>617</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>603</v>
+        <v>80</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>114</v>
+        <v>618</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>619</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>620</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>209</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>80</v>
       </c>
@@ -13869,19 +13897,19 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>103</v>
+        <v>622</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>122</v>
+        <v>623</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13890,10 +13918,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>105</v>
+        <v>625</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13904,10 +13932,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>672</v>
+        <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>672</v>
+        <v>626</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13915,35 +13943,33 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>281</v>
+        <v>618</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>673</v>
+        <v>627</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>674</v>
+        <v>628</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13967,13 +13993,13 @@
         <v>80</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>372</v>
+        <v>80</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>373</v>
+        <v>80</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>80</v>
@@ -13991,34 +14017,34 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>672</v>
+        <v>626</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>103</v>
+        <v>622</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>104</v>
+        <v>623</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>677</v>
+        <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>376</v>
+        <v>624</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>377</v>
+        <v>629</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>80</v>
@@ -14026,10 +14052,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14043,28 +14069,28 @@
         <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>460</v>
+        <v>281</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>679</v>
+        <v>631</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>680</v>
+        <v>632</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>681</v>
+        <v>633</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>463</v>
+        <v>634</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>80</v>
@@ -14089,13 +14115,13 @@
         <v>80</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>272</v>
+        <v>175</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>682</v>
+        <v>635</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>80</v>
@@ -14113,7 +14139,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14122,7 +14148,7 @@
         <v>91</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>684</v>
+        <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>104</v>
@@ -14131,27 +14157,27 @@
         <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>685</v>
+        <v>637</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>468</v>
+        <v>638</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>469</v>
+        <v>544</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>470</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14162,10 +14188,10 @@
         <v>78</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>80</v>
@@ -14177,16 +14203,16 @@
         <v>281</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>687</v>
+        <v>640</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>688</v>
+        <v>641</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>689</v>
+        <v>642</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>529</v>
+        <v>643</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>80</v>
@@ -14211,13 +14237,13 @@
         <v>80</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>530</v>
+        <v>644</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>531</v>
+        <v>645</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -14235,16 +14261,16 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>690</v>
+        <v>103</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>104</v>
@@ -14253,13 +14279,13 @@
         <v>80</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>80</v>
+        <v>637</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>105</v>
+        <v>638</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -14270,21 +14296,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>535</v>
+        <v>80</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>80</v>
@@ -14296,19 +14322,19 @@
         <v>80</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>281</v>
+        <v>647</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>536</v>
+        <v>648</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>537</v>
+        <v>649</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>538</v>
+        <v>650</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>539</v>
+        <v>651</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -14333,13 +14359,13 @@
         <v>80</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>540</v>
+        <v>80</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>692</v>
+        <v>80</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>80</v>
@@ -14357,45 +14383,45 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>104</v>
+        <v>652</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>542</v>
+        <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>543</v>
+        <v>653</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>544</v>
+        <v>654</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>693</v>
+        <v>655</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14406,7 +14432,7 @@
         <v>78</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>80</v>
@@ -14418,20 +14444,18 @@
         <v>80</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>694</v>
+        <v>656</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>695</v>
+        <v>657</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>80</v>
       </c>
@@ -14479,41 +14503,1373 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AG99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH99" t="s" s="2">
+      <c r="AA107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP99" t="s" s="2">
+      <c r="H109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP110" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP99">
+  <autoFilter ref="A1:AP110">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14523,7 +15879,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI109">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
